--- a/revolution-bio/redirects-tilda.xlsx
+++ b/revolution-bio/redirects-tilda.xlsx
@@ -532,21 +532,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -559,21 +555,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-cream</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара exo-boost-cream</t>
+          <t>Rejusome, окно товара exo-boost-cream (было /rejusome#p-exo-boost-cream, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -586,21 +578,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара rejusome</t>
+          <t>Rejusome, окно товара rejusome (было /rejusome#p-rejusome, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -613,21 +601,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара rejusome-plus</t>
+          <t>Rejusome, окно товара rejusome-plus (было /rejusome#p-rejusome-plus, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -640,21 +624,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/rejusome#p-rejusome-plus</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара rejusome-plus</t>
+          <t>Rejusome, окно товара rejusome-plus (было /rejusome#p-rejusome-plus, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -667,21 +647,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-serum</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара exo-boost-serum</t>
+          <t>Rejusome, окно товара exo-boost-serum (было /rejusome#p-exo-boost-serum, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -694,21 +670,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mask</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара exo-boost-mask</t>
+          <t>Rejusome, окно товара exo-boost-mask (было /rejusome#p-exo-boost-mask, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -721,21 +693,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/rejusome#p-exo-boost-mist</t>
+          <t>/rejusome</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rejusome, окно товара exo-boost-mist</t>
+          <t>Rejusome, окно товара exo-boost-mist (было /rejusome#p-exo-boost-mist, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /rejusome</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2252,21 +2220,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2279,21 +2243,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2306,21 +2266,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2333,21 +2289,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2360,21 +2312,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2387,21 +2335,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2414,21 +2358,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2441,21 +2381,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2468,21 +2404,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2495,21 +2427,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2522,21 +2450,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2549,21 +2473,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2576,21 +2496,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2603,21 +2519,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2630,21 +2542,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2657,21 +2565,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2684,21 +2588,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2711,21 +2611,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2738,21 +2634,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2765,21 +2657,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2792,21 +2680,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2819,21 +2703,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2846,21 +2726,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2873,21 +2749,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2900,7 +2772,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2910,13 +2782,13 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2803,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2941,13 +2813,13 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -2962,21 +2834,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2989,21 +2857,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3016,21 +2880,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3043,21 +2903,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3070,21 +2926,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3097,21 +2949,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3124,21 +2972,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3151,21 +2995,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3178,21 +3018,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3205,7 +3041,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3215,13 +3051,13 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3072,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3246,13 +3082,13 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3267,21 +3103,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3294,7 +3126,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3304,13 +3136,13 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3157,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3335,13 +3167,13 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3188,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3366,13 +3198,13 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3219,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3397,13 +3229,13 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3250,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3428,13 +3260,13 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3281,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3459,13 +3291,13 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3312,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3490,13 +3322,13 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3343,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3521,13 +3353,13 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3374,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3552,13 +3384,13 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3405,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3583,13 +3415,13 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3436,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3614,13 +3446,13 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3467,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3645,13 +3477,13 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3498,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3676,13 +3508,13 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3529,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3707,13 +3539,13 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3560,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3738,13 +3570,13 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3591,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3769,13 +3601,13 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3622,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3800,13 +3632,13 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3653,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3831,13 +3663,13 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3684,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3862,13 +3694,13 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3715,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3893,13 +3725,13 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3746,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3924,13 +3756,13 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3777,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3955,13 +3787,13 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3808,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3986,13 +3818,13 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4007,7 +3839,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4017,13 +3849,13 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4038,7 +3870,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4048,13 +3880,13 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4069,7 +3901,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4079,13 +3911,13 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4100,7 +3932,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4110,13 +3942,13 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4131,7 +3963,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4141,13 +3973,13 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4162,7 +3994,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4172,13 +4004,13 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»; Если Tilda не примет «#…», укажите адрес без него: /</t>
+          <t>Есть кириллица или пробел. Если Tilda не примет адрес, вставьте вариант из колонки «Старый адрес (закодированный)»</t>
         </is>
       </c>
     </row>
@@ -4193,21 +4025,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/#katalog</t>
+          <t>/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Главная, блок «Каталог»</t>
+          <t>Главная, блок «Каталог» (было /#katalog, Tilda не принимает «#»)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Если Tilda не примет «#…», укажите адрес без него: /</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
